--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.56138</v>
+        <v>16.89124</v>
       </c>
       <c r="D2" t="n">
-        <v>16.1341</v>
+        <v>17.09444</v>
       </c>
       <c r="E2" t="n">
-        <v>16.34206</v>
+        <v>16.9748</v>
       </c>
       <c r="F2" t="n">
-        <v>21.71868</v>
+        <v>42.86346</v>
       </c>
       <c r="G2" t="n">
-        <v>21.67314</v>
+        <v>0.05153</v>
       </c>
       <c r="H2" t="n">
-        <v>34.05754</v>
+        <v>1.84526</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.52627</v>
+        <v>16.82659</v>
       </c>
       <c r="D3" t="n">
-        <v>15.92225</v>
+        <v>16.32232</v>
       </c>
       <c r="E3" t="n">
-        <v>16.62613</v>
+        <v>16.33461</v>
       </c>
       <c r="F3" t="n">
-        <v>21.31203</v>
+        <v>4364.691</v>
       </c>
       <c r="G3" t="n">
-        <v>21.58066</v>
+        <v>0.05196</v>
       </c>
       <c r="H3" t="n">
-        <v>34.5833</v>
+        <v>1.86164</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.99564</v>
+        <v>16.94273</v>
       </c>
       <c r="D4" t="n">
-        <v>16.19538</v>
+        <v>16.6959</v>
       </c>
       <c r="E4" t="n">
-        <v>16.35241</v>
+        <v>16.78078</v>
       </c>
       <c r="F4" t="n">
-        <v>22.12516</v>
+        <v>42.17622</v>
       </c>
       <c r="G4" t="n">
-        <v>22.01065</v>
+        <v>0.05144</v>
       </c>
       <c r="H4" t="n">
-        <v>34.09372</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.84453</v>
+        <v>16.77385</v>
       </c>
       <c r="D5" t="n">
-        <v>15.89467</v>
+        <v>16.70001</v>
       </c>
       <c r="E5" t="n">
-        <v>16.56021</v>
+        <v>16.76573</v>
       </c>
       <c r="F5" t="n">
-        <v>21.65813</v>
+        <v>42.12316</v>
       </c>
       <c r="G5" t="n">
-        <v>22.52538</v>
+        <v>0.04978</v>
       </c>
       <c r="H5" t="n">
-        <v>35.23195</v>
+        <v>1.80699</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.40755</v>
+        <v>17.25794</v>
       </c>
       <c r="D6" t="n">
-        <v>16.11808</v>
+        <v>16.64477</v>
       </c>
       <c r="E6" t="n">
-        <v>16.54731</v>
+        <v>16.77994</v>
       </c>
       <c r="F6" t="n">
-        <v>21.95145</v>
+        <v>42.47729</v>
       </c>
       <c r="G6" t="n">
-        <v>21.54297</v>
+        <v>0.0507</v>
       </c>
       <c r="H6" t="n">
-        <v>34.31928</v>
+        <v>1.85741</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.51482</v>
+        <v>16.98674</v>
       </c>
       <c r="D7" t="n">
-        <v>15.86199</v>
+        <v>16.65671</v>
       </c>
       <c r="E7" t="n">
-        <v>16.49552</v>
+        <v>16.71498</v>
       </c>
       <c r="F7" t="n">
-        <v>21.67161</v>
+        <v>43.19667</v>
       </c>
       <c r="G7" t="n">
-        <v>21.70984</v>
+        <v>0.05135</v>
       </c>
       <c r="H7" t="n">
-        <v>34.45299</v>
+        <v>1.80934</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.54697</v>
+        <v>16.97864</v>
       </c>
       <c r="D8" t="n">
-        <v>16.63388</v>
+        <v>16.70104</v>
       </c>
       <c r="E8" t="n">
-        <v>16.16162</v>
+        <v>16.78927</v>
       </c>
       <c r="F8" t="n">
-        <v>21.92304</v>
+        <v>42.91109</v>
       </c>
       <c r="G8" t="n">
-        <v>21.97623</v>
+        <v>0.05029</v>
       </c>
       <c r="H8" t="n">
-        <v>34.64538</v>
+        <v>1.85351</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.74181</v>
+        <v>16.64125</v>
       </c>
       <c r="D9" t="n">
-        <v>15.9403</v>
+        <v>16.57964</v>
       </c>
       <c r="E9" t="n">
-        <v>16.15974</v>
+        <v>16.63247</v>
       </c>
       <c r="F9" t="n">
-        <v>22.14596</v>
+        <v>42.81385</v>
       </c>
       <c r="G9" t="n">
-        <v>22.2347</v>
+        <v>0.04971</v>
       </c>
       <c r="H9" t="n">
-        <v>33.76212</v>
+        <v>1.80546</v>
       </c>
     </row>
     <row r="10">
@@ -660,63 +660,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.80679</v>
+        <v>17.05845</v>
       </c>
       <c r="D10" t="n">
-        <v>15.93704</v>
+        <v>16.80923</v>
       </c>
       <c r="E10" t="n">
-        <v>16.55527</v>
+        <v>16.82714</v>
       </c>
       <c r="F10" t="n">
-        <v>21.93464</v>
+        <v>42.1722</v>
       </c>
       <c r="G10" t="n">
-        <v>21.69504</v>
+        <v>0.05109</v>
       </c>
       <c r="H10" t="n">
-        <v>34.71284</v>
+        <v>1.84731</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -728,32 +698,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.76278</v>
+        <v>0.59981</v>
       </c>
       <c r="D12" t="n">
-        <v>0.08210000000000001</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6224</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.96901</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.10869</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.00769</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.09103</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.12967</v>
+        <v>1.13046</v>
       </c>
     </row>
     <row r="13">
@@ -763,28 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.75753</v>
+        <v>0.6109599999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.08341</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.61291</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.93674</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.11012</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.09485</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.1275</v>
+        <v>1.12984</v>
       </c>
     </row>
     <row r="14">
@@ -794,28 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.74425</v>
+        <v>0.6036899999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07958</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.61541</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.95369</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.10969</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.09293999999999999</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.126</v>
+        <v>1.10789</v>
       </c>
     </row>
     <row r="15">
@@ -825,28 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.74916</v>
+        <v>0.61708</v>
       </c>
       <c r="D15" t="n">
-        <v>0.08083</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.61349</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.98015</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.1101</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09433999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.12681</v>
+        <v>1.11486</v>
       </c>
     </row>
     <row r="16">
@@ -856,28 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.75659</v>
+        <v>0.5974</v>
       </c>
       <c r="D16" t="n">
-        <v>0.08227</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.61205</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.98154</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.11082</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.00757</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.09352000000000001</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.12644</v>
+        <v>1.09428</v>
       </c>
     </row>
     <row r="17">
@@ -887,28 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7541</v>
+        <v>0.6102300000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0808</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.60309</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.95794</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.11044</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.09472999999999999</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.12844</v>
+        <v>1.13736</v>
       </c>
     </row>
     <row r="18">
@@ -918,28 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.74797</v>
+        <v>0.61529</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08162999999999999</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.60786</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.96336</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.11098</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09514</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.12871</v>
+        <v>1.12109</v>
       </c>
     </row>
     <row r="19">
@@ -949,28 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7552</v>
+        <v>0.62044</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0808</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.6001300000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.95396</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.10819</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.00778</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.09336999999999999</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.1251</v>
+        <v>1.12832</v>
       </c>
     </row>
     <row r="20">
@@ -980,28 +806,336 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7598200000000001</v>
+        <v>0.60724</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07935</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.6055</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.98531</v>
-      </c>
-      <c r="G20" t="n">
+        <v>1.12416</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.75887</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.08289000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.60403</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9770799999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.11118</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.09376</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.1284</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.08155</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9594</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.11129</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09564</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.12366</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.75514</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.08117000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9695</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.10973</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09368</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1268</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.75731</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.08042000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6067</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.98206</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.10704</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09386</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.12595</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7484499999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.61531</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.96462</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.10837</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09361</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.12792</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.75657</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.08237999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.61072</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.96922</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.10847</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.09361</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.12757</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.77642</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.08086</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6150099999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.95436</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.10793</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.09465999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.12889</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.08153000000000001</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.60843</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.11101</v>
       </c>
-      <c r="H20" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.09589</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.12525</v>
+      <c r="H29" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.09368</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.12943</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.75287</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08086</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.61732</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9446</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.11063</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.00772</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.09224</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1263</v>
       </c>
     </row>
   </sheetData>
